--- a/artfynd/A 13353-2025 artfynd.xlsx
+++ b/artfynd/A 13353-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123528269</v>
+        <v>123528106</v>
       </c>
       <c r="B2" t="n">
-        <v>57851</v>
+        <v>98379</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585267</v>
+        <v>585285</v>
       </c>
       <c r="R2" t="n">
-        <v>6404257</v>
+        <v>6404227</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123528106</v>
+        <v>123528317</v>
       </c>
       <c r="B3" t="n">
-        <v>98379</v>
+        <v>57497</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,35 +798,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585285</v>
+        <v>585305</v>
       </c>
       <c r="R3" t="n">
-        <v>6404227</v>
+        <v>6404272</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,7 +878,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123528274</v>
+        <v>123528269</v>
       </c>
       <c r="B4" t="n">
-        <v>58023</v>
+        <v>57851</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,16 +912,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102990</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1014,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123528146</v>
+        <v>123528489</v>
       </c>
       <c r="B5" t="n">
-        <v>98379</v>
+        <v>57634</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,35 +1022,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1062,13 +1062,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585263</v>
+        <v>585298</v>
       </c>
       <c r="R5" t="n">
-        <v>6404235</v>
+        <v>6404241</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1106,7 +1106,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1125,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123528221</v>
+        <v>123528146</v>
       </c>
       <c r="B6" t="n">
-        <v>92247</v>
+        <v>98379</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,34 +1136,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1172,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585259</v>
+        <v>585263</v>
       </c>
       <c r="R6" t="n">
-        <v>6404244</v>
+        <v>6404235</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123528317</v>
+        <v>123528221</v>
       </c>
       <c r="B7" t="n">
-        <v>57497</v>
+        <v>92247</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,35 +1247,34 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1283,10 +1282,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585305</v>
+        <v>585259</v>
       </c>
       <c r="R7" t="n">
-        <v>6404272</v>
+        <v>6404244</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,6 +1326,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1345,10 +1345,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123528489</v>
+        <v>123528274</v>
       </c>
       <c r="B8" t="n">
-        <v>57634</v>
+        <v>58023</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,37 +1357,37 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>102990</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585298</v>
+        <v>585267</v>
       </c>
       <c r="R8" t="n">
-        <v>6404241</v>
+        <v>6404257</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>

--- a/artfynd/A 13353-2025 artfynd.xlsx
+++ b/artfynd/A 13353-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123528106</v>
+        <v>123528221</v>
       </c>
       <c r="B2" t="n">
-        <v>98379</v>
+        <v>92264</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585285</v>
+        <v>585259</v>
       </c>
       <c r="R2" t="n">
-        <v>6404227</v>
+        <v>6404244</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123528317</v>
+        <v>123528489</v>
       </c>
       <c r="B3" t="n">
-        <v>57497</v>
+        <v>57640</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,29 +801,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -834,13 +837,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585305</v>
+        <v>585298</v>
       </c>
       <c r="R3" t="n">
-        <v>6404272</v>
+        <v>6404241</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -896,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123528269</v>
+        <v>123528146</v>
       </c>
       <c r="B4" t="n">
-        <v>57851</v>
+        <v>98396</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,39 +911,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -948,13 +947,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585267</v>
+        <v>585263</v>
       </c>
       <c r="R4" t="n">
-        <v>6404257</v>
+        <v>6404235</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,6 +991,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1010,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123528489</v>
+        <v>123528317</v>
       </c>
       <c r="B5" t="n">
-        <v>57634</v>
+        <v>57503</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,33 +1026,29 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1062,13 +1058,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585298</v>
+        <v>585305</v>
       </c>
       <c r="R5" t="n">
-        <v>6404241</v>
+        <v>6404272</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1124,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123528146</v>
+        <v>123528106</v>
       </c>
       <c r="B6" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1172,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585263</v>
+        <v>585285</v>
       </c>
       <c r="R6" t="n">
-        <v>6404235</v>
+        <v>6404227</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1235,10 +1231,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123528221</v>
+        <v>123528269</v>
       </c>
       <c r="B7" t="n">
-        <v>92247</v>
+        <v>57857</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,30 +1247,35 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1282,13 +1283,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585259</v>
+        <v>585267</v>
       </c>
       <c r="R7" t="n">
-        <v>6404244</v>
+        <v>6404257</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1326,7 +1327,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1348,7 +1348,7 @@
         <v>123528274</v>
       </c>
       <c r="B8" t="n">
-        <v>58023</v>
+        <v>58029</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 13353-2025 artfynd.xlsx
+++ b/artfynd/A 13353-2025 artfynd.xlsx
@@ -1120,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123528106</v>
+        <v>123528269</v>
       </c>
       <c r="B6" t="n">
-        <v>98396</v>
+        <v>57857</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,35 +1132,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1168,13 +1172,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585285</v>
+        <v>585267</v>
       </c>
       <c r="R6" t="n">
-        <v>6404227</v>
+        <v>6404257</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,7 +1216,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1231,10 +1234,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123528269</v>
+        <v>123528106</v>
       </c>
       <c r="B7" t="n">
-        <v>57857</v>
+        <v>98396</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1243,39 +1246,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1283,13 +1282,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585267</v>
+        <v>585285</v>
       </c>
       <c r="R7" t="n">
-        <v>6404257</v>
+        <v>6404227</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1327,6 +1326,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 13353-2025 artfynd.xlsx
+++ b/artfynd/A 13353-2025 artfynd.xlsx
@@ -1120,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123528269</v>
+        <v>123528106</v>
       </c>
       <c r="B6" t="n">
-        <v>57857</v>
+        <v>98396</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,39 +1132,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1172,13 +1168,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585267</v>
+        <v>585285</v>
       </c>
       <c r="R6" t="n">
-        <v>6404257</v>
+        <v>6404227</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,6 +1212,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1234,10 +1231,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123528106</v>
+        <v>123528269</v>
       </c>
       <c r="B7" t="n">
-        <v>98396</v>
+        <v>57857</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,35 +1243,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1282,13 +1283,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585285</v>
+        <v>585267</v>
       </c>
       <c r="R7" t="n">
-        <v>6404227</v>
+        <v>6404257</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1326,7 +1327,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 13353-2025 artfynd.xlsx
+++ b/artfynd/A 13353-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123528221</v>
+        <v>123528274</v>
       </c>
       <c r="B2" t="n">
-        <v>92264</v>
+        <v>58032</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,30 +691,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>102990</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585259</v>
+        <v>585267</v>
       </c>
       <c r="R2" t="n">
-        <v>6404244</v>
+        <v>6404257</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -766,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123528489</v>
+        <v>123528106</v>
       </c>
       <c r="B3" t="n">
-        <v>57640</v>
+        <v>98502</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,39 +801,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,13 +837,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585298</v>
+        <v>585285</v>
       </c>
       <c r="R3" t="n">
-        <v>6404241</v>
+        <v>6404227</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,6 +881,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -899,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123528146</v>
+        <v>123528489</v>
       </c>
       <c r="B4" t="n">
-        <v>98396</v>
+        <v>57643</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,35 +912,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -947,13 +952,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585263</v>
+        <v>585298</v>
       </c>
       <c r="R4" t="n">
-        <v>6404235</v>
+        <v>6404241</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,7 +996,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1010,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123528317</v>
+        <v>123528146</v>
       </c>
       <c r="B5" t="n">
-        <v>57503</v>
+        <v>98502</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,35 +1026,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1058,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585305</v>
+        <v>585263</v>
       </c>
       <c r="R5" t="n">
-        <v>6404272</v>
+        <v>6404235</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,6 +1106,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1120,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123528106</v>
+        <v>123528269</v>
       </c>
       <c r="B6" t="n">
-        <v>98396</v>
+        <v>57860</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,35 +1137,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1168,13 +1177,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585285</v>
+        <v>585267</v>
       </c>
       <c r="R6" t="n">
-        <v>6404227</v>
+        <v>6404257</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,7 +1221,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1231,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123528269</v>
+        <v>123528221</v>
       </c>
       <c r="B7" t="n">
-        <v>57857</v>
+        <v>92269</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,35 +1255,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1283,13 +1286,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585267</v>
+        <v>585259</v>
       </c>
       <c r="R7" t="n">
-        <v>6404257</v>
+        <v>6404244</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1327,6 +1330,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1345,10 +1349,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123528274</v>
+        <v>123528317</v>
       </c>
       <c r="B8" t="n">
-        <v>58029</v>
+        <v>57506</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,20 +1361,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102990</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1378,16 +1382,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1397,13 +1397,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585267</v>
+        <v>585305</v>
       </c>
       <c r="R8" t="n">
-        <v>6404257</v>
+        <v>6404272</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>

--- a/artfynd/A 13353-2025 artfynd.xlsx
+++ b/artfynd/A 13353-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123528274</v>
+        <v>123528221</v>
       </c>
       <c r="B2" t="n">
-        <v>58032</v>
+        <v>92271</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,35 +691,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102990</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585267</v>
+        <v>585259</v>
       </c>
       <c r="R2" t="n">
-        <v>6404257</v>
+        <v>6404244</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,6 +766,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123528106</v>
+        <v>123528146</v>
       </c>
       <c r="B3" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -837,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585285</v>
+        <v>585263</v>
       </c>
       <c r="R3" t="n">
-        <v>6404227</v>
+        <v>6404235</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123528489</v>
+        <v>123528269</v>
       </c>
       <c r="B4" t="n">
-        <v>57643</v>
+        <v>57861</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,37 +908,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -952,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585298</v>
+        <v>585267</v>
       </c>
       <c r="R4" t="n">
-        <v>6404241</v>
+        <v>6404257</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1014,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123528146</v>
+        <v>123528106</v>
       </c>
       <c r="B5" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1062,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585263</v>
+        <v>585285</v>
       </c>
       <c r="R5" t="n">
-        <v>6404235</v>
+        <v>6404227</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1125,10 +1121,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123528269</v>
+        <v>123528317</v>
       </c>
       <c r="B6" t="n">
-        <v>57860</v>
+        <v>57507</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,20 +1133,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1158,16 +1154,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1177,13 +1169,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585267</v>
+        <v>585305</v>
       </c>
       <c r="R6" t="n">
-        <v>6404257</v>
+        <v>6404272</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1239,10 +1231,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123528221</v>
+        <v>123528274</v>
       </c>
       <c r="B7" t="n">
-        <v>92269</v>
+        <v>58033</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1255,30 +1247,35 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>102990</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1286,13 +1283,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585259</v>
+        <v>585267</v>
       </c>
       <c r="R7" t="n">
-        <v>6404244</v>
+        <v>6404257</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1330,7 +1327,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1349,10 +1345,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123528317</v>
+        <v>123528489</v>
       </c>
       <c r="B8" t="n">
-        <v>57506</v>
+        <v>57644</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1365,29 +1361,33 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1397,13 +1397,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585305</v>
+        <v>585298</v>
       </c>
       <c r="R8" t="n">
-        <v>6404272</v>
+        <v>6404241</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>

--- a/artfynd/A 13353-2025 artfynd.xlsx
+++ b/artfynd/A 13353-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123528221</v>
+        <v>123528106</v>
       </c>
       <c r="B2" t="n">
-        <v>92271</v>
+        <v>98079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,34 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585259</v>
+        <v>585285</v>
       </c>
       <c r="R2" t="n">
-        <v>6404244</v>
+        <v>6404227</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123528146</v>
+        <v>123528274</v>
       </c>
       <c r="B3" t="n">
-        <v>98504</v>
+        <v>58033</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,35 +798,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>102990</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585263</v>
+        <v>585267</v>
       </c>
       <c r="R3" t="n">
-        <v>6404235</v>
+        <v>6404257</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,7 +882,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -896,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123528269</v>
+        <v>123528221</v>
       </c>
       <c r="B4" t="n">
-        <v>57861</v>
+        <v>92271</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,35 +916,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -948,13 +947,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585267</v>
+        <v>585259</v>
       </c>
       <c r="R4" t="n">
-        <v>6404257</v>
+        <v>6404244</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,6 +991,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1010,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123528106</v>
+        <v>123528489</v>
       </c>
       <c r="B5" t="n">
-        <v>98504</v>
+        <v>57644</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,35 +1022,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1058,13 +1062,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585285</v>
+        <v>585298</v>
       </c>
       <c r="R5" t="n">
-        <v>6404227</v>
+        <v>6404241</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1102,7 +1106,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1121,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123528317</v>
+        <v>123528269</v>
       </c>
       <c r="B6" t="n">
-        <v>57507</v>
+        <v>57861</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,20 +1136,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1154,12 +1157,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1169,13 +1176,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585305</v>
+        <v>585267</v>
       </c>
       <c r="R6" t="n">
-        <v>6404272</v>
+        <v>6404257</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1231,10 +1238,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123528274</v>
+        <v>123528146</v>
       </c>
       <c r="B7" t="n">
-        <v>58033</v>
+        <v>98079</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1243,39 +1250,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102990</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1283,13 +1286,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585267</v>
+        <v>585263</v>
       </c>
       <c r="R7" t="n">
-        <v>6404257</v>
+        <v>6404235</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1327,6 +1330,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1345,10 +1349,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123528489</v>
+        <v>123528317</v>
       </c>
       <c r="B8" t="n">
-        <v>57644</v>
+        <v>57507</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1361,33 +1365,29 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1397,13 +1397,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585298</v>
+        <v>585305</v>
       </c>
       <c r="R8" t="n">
-        <v>6404241</v>
+        <v>6404272</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>

--- a/artfynd/A 13353-2025 artfynd.xlsx
+++ b/artfynd/A 13353-2025 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123528274</v>
+        <v>123528221</v>
       </c>
       <c r="B3" t="n">
-        <v>58033</v>
+        <v>92271</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,35 +802,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102990</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,13 +833,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585267</v>
+        <v>585259</v>
       </c>
       <c r="R3" t="n">
-        <v>6404257</v>
+        <v>6404244</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,6 +877,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123528221</v>
+        <v>123528489</v>
       </c>
       <c r="B4" t="n">
-        <v>92271</v>
+        <v>57644</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,34 +908,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -947,13 +948,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585259</v>
+        <v>585298</v>
       </c>
       <c r="R4" t="n">
-        <v>6404244</v>
+        <v>6404241</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,7 +992,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1010,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123528489</v>
+        <v>123528274</v>
       </c>
       <c r="B5" t="n">
-        <v>57644</v>
+        <v>58033</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,37 +1022,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>102990</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585298</v>
+        <v>585267</v>
       </c>
       <c r="R5" t="n">
-        <v>6404241</v>
+        <v>6404257</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1124,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123528269</v>
+        <v>123528317</v>
       </c>
       <c r="B6" t="n">
-        <v>57861</v>
+        <v>57507</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1136,20 +1136,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1157,16 +1157,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1176,13 +1172,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585267</v>
+        <v>585305</v>
       </c>
       <c r="R6" t="n">
-        <v>6404257</v>
+        <v>6404272</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1349,10 +1345,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123528317</v>
+        <v>123528269</v>
       </c>
       <c r="B8" t="n">
-        <v>57507</v>
+        <v>57861</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1361,20 +1357,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1382,12 +1378,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1397,13 +1397,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585305</v>
+        <v>585267</v>
       </c>
       <c r="R8" t="n">
-        <v>6404272</v>
+        <v>6404257</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>

--- a/artfynd/A 13353-2025 artfynd.xlsx
+++ b/artfynd/A 13353-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123528106</v>
+        <v>123528489</v>
       </c>
       <c r="B2" t="n">
-        <v>98079</v>
+        <v>57644</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585285</v>
+        <v>585298</v>
       </c>
       <c r="R2" t="n">
-        <v>6404227</v>
+        <v>6404241</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -767,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -786,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123528221</v>
+        <v>123528274</v>
       </c>
       <c r="B3" t="n">
-        <v>92271</v>
+        <v>58033</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,30 +805,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>102990</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585259</v>
+        <v>585267</v>
       </c>
       <c r="R3" t="n">
-        <v>6404244</v>
+        <v>6404257</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,7 +885,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -896,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123528489</v>
+        <v>123528146</v>
       </c>
       <c r="B4" t="n">
-        <v>57644</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,39 +915,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -948,13 +951,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585298</v>
+        <v>585263</v>
       </c>
       <c r="R4" t="n">
-        <v>6404241</v>
+        <v>6404235</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,6 +995,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1010,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123528274</v>
+        <v>123528269</v>
       </c>
       <c r="B5" t="n">
-        <v>58033</v>
+        <v>57861</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,16 +1030,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102990</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1124,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123528317</v>
+        <v>123528106</v>
       </c>
       <c r="B6" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1136,35 +1140,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1172,10 +1176,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585305</v>
+        <v>585285</v>
       </c>
       <c r="R6" t="n">
-        <v>6404272</v>
+        <v>6404227</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,6 +1220,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1234,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123528146</v>
+        <v>123528221</v>
       </c>
       <c r="B7" t="n">
-        <v>98079</v>
+        <v>92271</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,35 +1251,34 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1282,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585263</v>
+        <v>585259</v>
       </c>
       <c r="R7" t="n">
-        <v>6404235</v>
+        <v>6404244</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,10 +1349,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123528269</v>
+        <v>123528317</v>
       </c>
       <c r="B8" t="n">
-        <v>57861</v>
+        <v>57507</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,20 +1361,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1378,16 +1382,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1397,13 +1397,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585267</v>
+        <v>585305</v>
       </c>
       <c r="R8" t="n">
-        <v>6404257</v>
+        <v>6404272</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>

--- a/artfynd/A 13353-2025 artfynd.xlsx
+++ b/artfynd/A 13353-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123528489</v>
+        <v>123528269</v>
       </c>
       <c r="B2" t="n">
-        <v>57644</v>
+        <v>57861</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,37 +687,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585298</v>
+        <v>585267</v>
       </c>
       <c r="R2" t="n">
-        <v>6404241</v>
+        <v>6404257</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123528274</v>
+        <v>123528221</v>
       </c>
       <c r="B3" t="n">
-        <v>58033</v>
+        <v>92271</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,35 +805,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102990</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -841,13 +836,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585267</v>
+        <v>585259</v>
       </c>
       <c r="R3" t="n">
-        <v>6404257</v>
+        <v>6404244</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,6 +880,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1014,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123528269</v>
+        <v>123528274</v>
       </c>
       <c r="B5" t="n">
-        <v>57861</v>
+        <v>58033</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,16 +1026,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>102990</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1128,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123528106</v>
+        <v>123528489</v>
       </c>
       <c r="B6" t="n">
-        <v>98079</v>
+        <v>57644</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,35 +1136,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1176,13 +1176,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585285</v>
+        <v>585298</v>
       </c>
       <c r="R6" t="n">
-        <v>6404227</v>
+        <v>6404241</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1220,7 +1220,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1239,10 +1238,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123528221</v>
+        <v>123528317</v>
       </c>
       <c r="B7" t="n">
-        <v>92271</v>
+        <v>57507</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,34 +1250,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585259</v>
+        <v>585305</v>
       </c>
       <c r="R7" t="n">
-        <v>6404244</v>
+        <v>6404272</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1330,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1349,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123528317</v>
+        <v>123528106</v>
       </c>
       <c r="B8" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1361,35 +1360,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1397,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585305</v>
+        <v>585285</v>
       </c>
       <c r="R8" t="n">
-        <v>6404272</v>
+        <v>6404227</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1441,6 +1440,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 13353-2025 artfynd.xlsx
+++ b/artfynd/A 13353-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123528269</v>
+        <v>123528106</v>
       </c>
       <c r="B2" t="n">
-        <v>57861</v>
+        <v>98079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585267</v>
+        <v>585285</v>
       </c>
       <c r="R2" t="n">
-        <v>6404257</v>
+        <v>6404227</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123528221</v>
+        <v>123528274</v>
       </c>
       <c r="B3" t="n">
-        <v>92271</v>
+        <v>58033</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,30 +802,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>102990</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -836,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585259</v>
+        <v>585267</v>
       </c>
       <c r="R3" t="n">
-        <v>6404244</v>
+        <v>6404257</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,7 +882,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -899,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123528146</v>
+        <v>123528269</v>
       </c>
       <c r="B4" t="n">
-        <v>98079</v>
+        <v>57861</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,35 +912,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -947,13 +952,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585263</v>
+        <v>585267</v>
       </c>
       <c r="R4" t="n">
-        <v>6404235</v>
+        <v>6404257</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,7 +996,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1010,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123528274</v>
+        <v>123528489</v>
       </c>
       <c r="B5" t="n">
-        <v>58033</v>
+        <v>57644</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,37 +1026,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102990</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1062,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585267</v>
+        <v>585298</v>
       </c>
       <c r="R5" t="n">
-        <v>6404257</v>
+        <v>6404241</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1124,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123528489</v>
+        <v>123528317</v>
       </c>
       <c r="B6" t="n">
-        <v>57644</v>
+        <v>57507</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,33 +1144,29 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1176,13 +1176,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585298</v>
+        <v>585305</v>
       </c>
       <c r="R6" t="n">
-        <v>6404241</v>
+        <v>6404272</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1238,10 +1238,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123528317</v>
+        <v>123528146</v>
       </c>
       <c r="B7" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,35 +1250,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585305</v>
+        <v>585263</v>
       </c>
       <c r="R7" t="n">
-        <v>6404272</v>
+        <v>6404235</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,6 +1330,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1348,10 +1349,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123528106</v>
+        <v>123528221</v>
       </c>
       <c r="B8" t="n">
-        <v>98079</v>
+        <v>92271</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,35 +1361,34 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1396,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585285</v>
+        <v>585259</v>
       </c>
       <c r="R8" t="n">
-        <v>6404227</v>
+        <v>6404244</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
